--- a/仕様書/プロト仕様書-プログラマ-.xlsx
+++ b/仕様書/プロト仕様書-プログラマ-.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanat\Desktop\MagnetRush\仕様書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC70447-9029-4E87-BBEF-7C003D625B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B1647D-C405-4819-A849-26178027B88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体ガント" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="382">
   <si>
     <t>← 全体ガントに戻る</t>
   </si>
@@ -1429,12 +1429,62 @@
     <t>Additive Scene</t>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>西川</t>
+    <rPh sb="0" eb="2">
+      <t>ニシカワ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>西川</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>着手中</t>
+    <rPh sb="0" eb="2">
+      <t>チャクシュ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>着手中</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>未着手</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>完了(仮)</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1658,6 +1708,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1846,7 +1914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1920,20 +1988,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2031,6 +2085,35 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2352,32 +2435,32 @@
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="36" t="s">
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="33"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="67"/>
     </row>
     <row r="2" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
@@ -2835,10 +2918,10 @@
       <c r="B2" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="42" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2849,10 +2932,10 @@
       <c r="B3" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="42" t="s">
         <v>305</v>
       </c>
     </row>
@@ -2863,10 +2946,10 @@
       <c r="B4" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="42" t="s">
         <v>308</v>
       </c>
     </row>
@@ -2877,10 +2960,10 @@
       <c r="B5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="42" t="s">
         <v>310</v>
       </c>
     </row>
@@ -2891,10 +2974,10 @@
       <c r="B6" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="42" t="s">
         <v>313</v>
       </c>
     </row>
@@ -2905,10 +2988,10 @@
       <c r="B7" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="42" t="s">
         <v>316</v>
       </c>
     </row>
@@ -2919,10 +3002,10 @@
       <c r="B8" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="42" t="s">
         <v>318</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="42" t="s">
         <v>319</v>
       </c>
     </row>
@@ -2933,10 +3016,10 @@
       <c r="B9" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="42" t="s">
         <v>321</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="42" t="s">
         <v>322</v>
       </c>
     </row>
@@ -2947,10 +3030,10 @@
       <c r="B10" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="42" t="s">
         <v>324</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="42" t="s">
         <v>325</v>
       </c>
     </row>
@@ -2961,20 +3044,20 @@
       <c r="B11" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="42" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="74"/>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="26" t="s">
@@ -2997,10 +3080,10 @@
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="43" t="s">
         <v>333</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="43" t="s">
         <v>334</v>
       </c>
     </row>
@@ -3011,10 +3094,10 @@
       <c r="B17" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="43" t="s">
         <v>335</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="43" t="s">
         <v>336</v>
       </c>
     </row>
@@ -3025,10 +3108,10 @@
       <c r="B18" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="43" t="s">
         <v>338</v>
       </c>
     </row>
@@ -3039,10 +3122,10 @@
       <c r="B19" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="43" t="s">
         <v>340</v>
       </c>
     </row>
@@ -3053,10 +3136,10 @@
       <c r="B20" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="43" t="s">
         <v>342</v>
       </c>
     </row>
@@ -3067,10 +3150,10 @@
       <c r="B21" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="43" t="s">
         <v>344</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="43" t="s">
         <v>345</v>
       </c>
     </row>
@@ -3081,10 +3164,10 @@
       <c r="B22" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="43" t="s">
         <v>347</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="43" t="s">
         <v>348</v>
       </c>
     </row>
@@ -3095,10 +3178,10 @@
       <c r="B23" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="43" t="s">
         <v>349</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="43" t="s">
         <v>350</v>
       </c>
     </row>
@@ -3109,10 +3192,10 @@
       <c r="B24" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="43" t="s">
         <v>352</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="43" t="s">
         <v>353</v>
       </c>
     </row>
@@ -3123,10 +3206,10 @@
       <c r="B25" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="43" t="s">
         <v>355</v>
       </c>
     </row>
@@ -3137,10 +3220,10 @@
       <c r="B26" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="43" t="s">
         <v>356</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="43" t="s">
         <v>357</v>
       </c>
     </row>
@@ -3176,33 +3259,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3236,70 +3319,70 @@
       <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3307,27 +3390,29 @@
       <c r="A3" s="14">
         <v>1</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="47" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="32" t="s">
         <v>361</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="69"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="75" t="s">
+        <v>374</v>
+      </c>
+      <c r="I3" s="75" t="s">
+        <v>376</v>
+      </c>
+      <c r="J3" s="59"/>
       <c r="K3" s="6"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -3355,29 +3440,31 @@
       <c r="A4" s="18">
         <v>2</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="33" t="s">
         <v>359</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="69"/>
+      <c r="H4" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I4" s="77" t="s">
+        <v>377</v>
+      </c>
+      <c r="J4" s="59"/>
       <c r="K4" s="6"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -3405,29 +3492,31 @@
       <c r="A5" s="18">
         <v>3</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="69"/>
+      <c r="H5" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I5" s="77" t="s">
+        <v>377</v>
+      </c>
+      <c r="J5" s="59"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="2"/>
@@ -3455,29 +3544,31 @@
       <c r="A6" s="18">
         <v>4</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="31" t="s">
         <v>360</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="70" t="s">
+      <c r="H6" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I6" s="77" t="s">
+        <v>380</v>
+      </c>
+      <c r="J6" s="60" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="2"/>
@@ -3507,29 +3598,31 @@
       <c r="A7" s="18">
         <v>5</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="35" t="s">
         <v>363</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="69"/>
+      <c r="H7" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I7" s="77" t="s">
+        <v>379</v>
+      </c>
+      <c r="J7" s="59"/>
       <c r="K7" s="2"/>
       <c r="L7" s="6"/>
       <c r="M7" s="2"/>
@@ -3557,29 +3650,31 @@
       <c r="A8" s="18">
         <v>6</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="36" t="s">
         <v>364</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="69"/>
+      <c r="H8" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I8" s="76" t="s">
+        <v>378</v>
+      </c>
+      <c r="J8" s="59"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -3607,29 +3702,31 @@
       <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="65" t="s">
+      <c r="G9" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="70" t="s">
+      <c r="H9" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I9" s="75" t="s">
+        <v>376</v>
+      </c>
+      <c r="J9" s="60" t="s">
         <v>50</v>
       </c>
       <c r="K9" s="2"/>
@@ -3659,29 +3756,31 @@
       <c r="A10" s="18">
         <v>8</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="33" t="s">
         <v>366</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="69"/>
+      <c r="H10" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I10" s="76" t="s">
+        <v>376</v>
+      </c>
+      <c r="J10" s="59"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="6"/>
@@ -3709,29 +3808,31 @@
       <c r="A11" s="18">
         <v>9</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="70" t="s">
+      <c r="H11" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I11" s="77" t="s">
+        <v>380</v>
+      </c>
+      <c r="J11" s="60" t="s">
         <v>44</v>
       </c>
       <c r="K11" s="2"/>
@@ -3761,29 +3862,31 @@
       <c r="A12" s="18">
         <v>10</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61" t="s">
+      <c r="H12" s="76" t="s">
+        <v>375</v>
+      </c>
+      <c r="I12" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="69"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -3866,33 +3969,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3926,70 +4029,70 @@
       <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4000,19 +4103,19 @@
       <c r="B3" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="63"/>
+      <c r="G3" s="53"/>
       <c r="H3" s="14"/>
       <c r="I3" s="14" t="s">
         <v>36</v>
@@ -4048,26 +4151,26 @@
       <c r="B4" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="69"/>
+      <c r="J4" s="59"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -4098,26 +4201,26 @@
       <c r="B5" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -4148,24 +4251,24 @@
       <c r="B6" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="70" t="s">
+      <c r="J6" s="60" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="2"/>
@@ -4198,26 +4301,26 @@
       <c r="B7" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61" t="s">
+      <c r="H7" s="51"/>
+      <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -4248,26 +4351,26 @@
       <c r="B8" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="65" t="s">
+      <c r="G8" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59" t="s">
+      <c r="H8" s="49"/>
+      <c r="I8" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="69"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -4298,26 +4401,26 @@
       <c r="B9" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61" t="s">
+      <c r="H9" s="51"/>
+      <c r="I9" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="70" t="s">
+      <c r="J9" s="60" t="s">
         <v>99</v>
       </c>
       <c r="K9" s="2"/>
@@ -4350,26 +4453,26 @@
       <c r="B10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="70" t="s">
+      <c r="J10" s="60" t="s">
         <v>103</v>
       </c>
       <c r="K10" s="2"/>
@@ -4402,26 +4505,26 @@
       <c r="B11" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="66" t="s">
+      <c r="E11" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61" t="s">
+      <c r="H11" s="51"/>
+      <c r="I11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="69"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -4452,26 +4555,26 @@
       <c r="B12" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="65" t="s">
+      <c r="G12" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59" t="s">
+      <c r="H12" s="49"/>
+      <c r="I12" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="69"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -4502,26 +4605,26 @@
       <c r="B13" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61" t="s">
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="69"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -4552,26 +4655,26 @@
       <c r="B14" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="51"/>
+      <c r="I14" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="69"/>
+      <c r="J14" s="59"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -4602,26 +4705,26 @@
       <c r="B15" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="65" t="s">
+      <c r="G15" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59" t="s">
+      <c r="H15" s="49"/>
+      <c r="I15" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="69"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -4652,26 +4755,26 @@
       <c r="B16" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61" t="s">
+      <c r="H16" s="51"/>
+      <c r="I16" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="69"/>
+      <c r="J16" s="59"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -4761,33 +4864,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4821,70 +4924,70 @@
       <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4895,24 +4998,24 @@
       <c r="B3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="69"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="78" t="s">
+        <v>376</v>
+      </c>
+      <c r="J3" s="59"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="2"/>
@@ -4943,26 +5046,26 @@
       <c r="B4" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59" t="s">
+      <c r="H4" s="49"/>
+      <c r="I4" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="69"/>
+      <c r="J4" s="59"/>
       <c r="K4" s="2"/>
       <c r="L4" s="6"/>
       <c r="M4" s="2"/>
@@ -4993,26 +5096,26 @@
       <c r="B5" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="2"/>
       <c r="L5" s="6"/>
       <c r="M5" s="2"/>
@@ -5043,26 +5146,26 @@
       <c r="B6" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="65" t="s">
+      <c r="G6" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59" t="s">
+      <c r="H6" s="49"/>
+      <c r="I6" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="2"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -5093,26 +5196,26 @@
       <c r="B7" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61" t="s">
+      <c r="H7" s="51"/>
+      <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="6"/>
@@ -5143,26 +5246,26 @@
       <c r="B8" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61" t="s">
+      <c r="H8" s="51"/>
+      <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="69"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="6"/>
@@ -5193,24 +5296,24 @@
       <c r="B9" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="63"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59" t="s">
+      <c r="G9" s="53"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="69"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="6"/>
@@ -5241,26 +5344,26 @@
       <c r="B10" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="69"/>
+      <c r="J10" s="59"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="6"/>
@@ -5291,26 +5394,26 @@
       <c r="B11" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="60" t="s">
+      <c r="E11" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61" t="s">
+      <c r="H11" s="51"/>
+      <c r="I11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="69"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -5341,26 +5444,26 @@
       <c r="B12" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61" t="s">
+      <c r="H12" s="51"/>
+      <c r="I12" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="69"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -5391,26 +5494,26 @@
       <c r="B13" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61" t="s">
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="69"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -5441,26 +5544,26 @@
       <c r="B14" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="51"/>
+      <c r="I14" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="69"/>
+      <c r="J14" s="59"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -5491,26 +5594,26 @@
       <c r="B15" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="E15" s="66" t="s">
+      <c r="E15" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="61" t="s">
+      <c r="F15" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61" t="s">
+      <c r="H15" s="51"/>
+      <c r="I15" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="69"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -5595,33 +5698,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5679,46 +5782,46 @@
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5729,7 +5832,7 @@
       <c r="B3" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="64" t="s">
         <v>160</v>
       </c>
       <c r="D3" s="22" t="s">
@@ -5743,8 +5846,8 @@
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="14"/>
-      <c r="I3" s="14" t="s">
-        <v>36</v>
+      <c r="I3" s="79" t="s">
+        <v>376</v>
       </c>
       <c r="J3" s="30" t="s">
         <v>44</v>
@@ -5779,26 +5882,26 @@
       <c r="B4" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="55" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="70" t="s">
+      <c r="H4" s="49"/>
+      <c r="I4" s="75" t="s">
+        <v>376</v>
+      </c>
+      <c r="J4" s="60" t="s">
         <v>165</v>
       </c>
       <c r="K4" s="6"/>
@@ -5831,26 +5934,26 @@
       <c r="B5" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="60" t="s">
         <v>169</v>
       </c>
       <c r="K5" s="2"/>
@@ -5883,26 +5986,26 @@
       <c r="B6" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="6"/>
@@ -5933,26 +6036,26 @@
       <c r="B7" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61" t="s">
+      <c r="H7" s="51"/>
+      <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="6"/>
@@ -5983,26 +6086,26 @@
       <c r="B8" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61" t="s">
+      <c r="H8" s="51"/>
+      <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="69"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -6033,26 +6136,26 @@
       <c r="B9" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="E9" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61" t="s">
+      <c r="H9" s="51"/>
+      <c r="I9" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="69"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -6083,26 +6186,26 @@
       <c r="B10" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="65" t="s">
+      <c r="G10" s="55" t="s">
         <v>184</v>
       </c>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59" t="s">
+      <c r="H10" s="49"/>
+      <c r="I10" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="69"/>
+      <c r="J10" s="59"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -6133,26 +6236,26 @@
       <c r="B11" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="60" t="s">
+      <c r="E11" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="54" t="s">
         <v>187</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61" t="s">
+      <c r="H11" s="51"/>
+      <c r="I11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="70" t="s">
+      <c r="J11" s="60" t="s">
         <v>188</v>
       </c>
       <c r="K11" s="2"/>
@@ -6185,24 +6288,24 @@
       <c r="B12" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59" t="s">
+      <c r="G12" s="53"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="69"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -6233,26 +6336,26 @@
       <c r="B13" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="34" t="s">
         <v>369</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61" t="s">
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="70" t="s">
+      <c r="J13" s="60" t="s">
         <v>165</v>
       </c>
       <c r="K13" s="2"/>
@@ -6285,26 +6388,26 @@
       <c r="B14" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="51"/>
+      <c r="I14" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="69"/>
+      <c r="J14" s="59"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -6335,26 +6438,26 @@
       <c r="B15" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="E15" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="61" t="s">
+      <c r="F15" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61" t="s">
+      <c r="H15" s="51"/>
+      <c r="I15" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="69"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -6385,26 +6488,26 @@
       <c r="B16" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="65" t="s">
+      <c r="G16" s="55" t="s">
         <v>184</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="59" t="s">
+      <c r="H16" s="49"/>
+      <c r="I16" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="70" t="s">
+      <c r="J16" s="60" t="s">
         <v>202</v>
       </c>
       <c r="K16" s="2"/>
@@ -6437,26 +6540,26 @@
       <c r="B17" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="62" t="s">
+      <c r="E17" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="F17" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61" t="s">
+      <c r="H17" s="51"/>
+      <c r="I17" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="69"/>
+      <c r="J17" s="59"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -6487,24 +6590,24 @@
       <c r="B18" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="E18" s="68" t="s">
+      <c r="E18" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="63"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59" t="s">
+      <c r="G18" s="53"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="69"/>
+      <c r="J18" s="59"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -6535,26 +6638,26 @@
       <c r="B19" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="C19" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="E19" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61" t="s">
+      <c r="H19" s="51"/>
+      <c r="I19" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="69"/>
+      <c r="J19" s="59"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -6585,26 +6688,26 @@
       <c r="B20" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="62" t="s">
+      <c r="E20" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61" t="s">
+      <c r="H20" s="51"/>
+      <c r="I20" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J20" s="69"/>
+      <c r="J20" s="59"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -6632,27 +6735,27 @@
       <c r="A21" s="14">
         <v>56</v>
       </c>
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="61" t="s">
         <v>372</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="E21" s="68" t="s">
+      <c r="E21" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="63"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59" t="s">
+      <c r="G21" s="53"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J21" s="69"/>
+      <c r="J21" s="59"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -6683,24 +6786,24 @@
       <c r="B22" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="61" t="s">
+      <c r="F22" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="67"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61" t="s">
+      <c r="G22" s="57"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="69"/>
+      <c r="J22" s="59"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -6731,26 +6834,26 @@
       <c r="B23" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="E23" s="66" t="s">
+      <c r="E23" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="61" t="s">
+      <c r="F23" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61" t="s">
+      <c r="H23" s="51"/>
+      <c r="I23" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="69"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -6854,33 +6957,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6914,70 +7017,70 @@
       <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6988,24 +7091,24 @@
       <c r="B3" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="63"/>
+      <c r="G3" s="53"/>
       <c r="H3" s="14"/>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="70" t="s">
+      <c r="J3" s="60" t="s">
         <v>235</v>
       </c>
       <c r="K3" s="2"/>
@@ -7038,24 +7141,24 @@
       <c r="B4" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="67"/>
+      <c r="G4" s="57"/>
       <c r="H4" s="18"/>
-      <c r="I4" s="61" t="s">
+      <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="69"/>
+      <c r="J4" s="59"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="6"/>
@@ -7086,26 +7189,26 @@
       <c r="B5" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="46" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="54" t="s">
         <v>240</v>
       </c>
       <c r="H5" s="18"/>
-      <c r="I5" s="61" t="s">
+      <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="60" t="s">
         <v>44</v>
       </c>
       <c r="K5" s="2"/>
@@ -7138,26 +7241,26 @@
       <c r="B6" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>243</v>
       </c>
       <c r="H6" s="18"/>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -7188,26 +7291,26 @@
       <c r="B7" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>246</v>
       </c>
       <c r="H7" s="18"/>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="70" t="s">
+      <c r="J7" s="60" t="s">
         <v>165</v>
       </c>
       <c r="K7" s="2"/>
@@ -7240,26 +7343,26 @@
       <c r="B8" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="46" t="s">
         <v>247</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="54" t="s">
         <v>249</v>
       </c>
       <c r="H8" s="18"/>
-      <c r="I8" s="61" t="s">
+      <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="69"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -7290,26 +7393,26 @@
       <c r="B9" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="64" t="s">
         <v>251</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="65" t="s">
+      <c r="G9" s="55" t="s">
         <v>253</v>
       </c>
       <c r="H9" s="14"/>
-      <c r="I9" s="59" t="s">
+      <c r="I9" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="69"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -7340,26 +7443,26 @@
       <c r="B10" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="54" t="s">
         <v>255</v>
       </c>
       <c r="H10" s="18"/>
-      <c r="I10" s="61" t="s">
+      <c r="I10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="70" t="s">
+      <c r="J10" s="60" t="s">
         <v>165</v>
       </c>
       <c r="K10" s="2"/>
@@ -7392,26 +7495,26 @@
       <c r="B11" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="45" t="s">
         <v>256</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="E11" s="66" t="s">
+      <c r="E11" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="54" t="s">
         <v>198</v>
       </c>
       <c r="H11" s="18"/>
-      <c r="I11" s="61" t="s">
+      <c r="I11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="69"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -7442,24 +7545,24 @@
       <c r="B12" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="64" t="s">
         <v>259</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59" t="s">
+      <c r="G12" s="53"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="69"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -7490,26 +7593,26 @@
       <c r="B13" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="45" t="s">
         <v>261</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="E13" s="62" t="s">
+      <c r="E13" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61" t="s">
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="70" t="s">
+      <c r="J13" s="60" t="s">
         <v>44</v>
       </c>
       <c r="K13" s="2"/>
@@ -7542,26 +7645,26 @@
       <c r="B14" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="E14" s="62" t="s">
+      <c r="E14" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="51"/>
+      <c r="I14" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="70" t="s">
+      <c r="J14" s="60" t="s">
         <v>165</v>
       </c>
       <c r="K14" s="2"/>
@@ -7594,26 +7697,26 @@
       <c r="B15" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="46" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="61" t="s">
+      <c r="F15" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61" t="s">
+      <c r="H15" s="51"/>
+      <c r="I15" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="69"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -7703,33 +7806,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7763,70 +7866,70 @@
       <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7837,24 +7940,24 @@
       <c r="B3" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59" t="s">
+      <c r="G3" s="53"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="69"/>
+      <c r="J3" s="59"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -7885,26 +7988,26 @@
       <c r="B4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="69"/>
+      <c r="J4" s="59"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -7935,24 +8038,24 @@
       <c r="B5" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="67"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="G5" s="57"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -7983,26 +8086,26 @@
       <c r="B6" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -8027,7 +8130,7 @@
       <c r="AF6" s="2"/>
     </row>
     <row r="7" spans="1:32" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="D7" s="50"/>
+      <c r="D7" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8072,33 +8175,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8132,70 +8235,70 @@
       <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8206,24 +8309,24 @@
       <c r="B3" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="64" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="41" t="s">
         <v>370</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="69"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="75" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="59"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -8254,26 +8357,26 @@
       <c r="B4" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="45" t="s">
         <v>271</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="E4" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="69"/>
+      <c r="J4" s="59"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -8304,26 +8407,26 @@
       <c r="B5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="45" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="62" t="s">
+      <c r="E5" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -8354,26 +8457,26 @@
       <c r="B6" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>278</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -8404,26 +8507,26 @@
       <c r="B7" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61" t="s">
+      <c r="H7" s="51"/>
+      <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -8454,26 +8557,26 @@
       <c r="B8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61" t="s">
+      <c r="H8" s="51"/>
+      <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="70" t="s">
+      <c r="J8" s="60" t="s">
         <v>283</v>
       </c>
       <c r="K8" s="2"/>
@@ -8548,33 +8651,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="33"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="67"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8617,61 +8720,61 @@
       <c r="M2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="72" t="s">
+      <c r="O2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="72" t="s">
+      <c r="Q2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="72" t="s">
+      <c r="U2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="72" t="s">
+      <c r="V2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="72" t="s">
+      <c r="W2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="72" t="s">
+      <c r="X2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="72" t="s">
+      <c r="Y2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="73" t="s">
+      <c r="AA2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="72" t="s">
+      <c r="AB2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="72" t="s">
+      <c r="AC2" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="72" t="s">
+      <c r="AD2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="72" t="s">
+      <c r="AE2" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="72" t="s">
+      <c r="AF2" s="62" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8682,24 +8785,24 @@
       <c r="B3" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59" t="s">
+      <c r="G3" s="53"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="69"/>
+      <c r="J3" s="59"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -8730,26 +8833,26 @@
       <c r="B4" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="E4" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="54" t="s">
         <v>289</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="70" t="s">
+      <c r="J4" s="60" t="s">
         <v>103</v>
       </c>
       <c r="K4" s="2"/>
@@ -8782,26 +8885,26 @@
       <c r="B5" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="44" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="55" t="s">
         <v>293</v>
       </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59" t="s">
+      <c r="H5" s="49"/>
+      <c r="I5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -8832,26 +8935,26 @@
       <c r="B6" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -8882,26 +8985,26 @@
       <c r="B7" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="E7" s="66" t="s">
+      <c r="E7" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61" t="s">
+      <c r="H7" s="51"/>
+      <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>

--- a/仕様書/プロト仕様書-プログラマ-.xlsx
+++ b/仕様書/プロト仕様書-プログラマ-.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanat\Desktop\MagnetRush\仕様書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B1647D-C405-4819-A849-26178027B88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197A9861-AAC8-4C7B-855A-E01CB732CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="4320" windowWidth="21600" windowHeight="11835" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体ガント" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="384">
   <si>
     <t>← 全体ガントに戻る</t>
   </si>
@@ -1479,12 +1479,22 @@
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>西郡</t>
+  </si>
+  <si>
+    <t>西郡</t>
+    <rPh sb="0" eb="2">
+      <t>ニシゴオリ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1726,6 +1736,12 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1914,7 +1930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2086,6 +2102,21 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -2100,19 +2131,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2435,32 +2454,32 @@
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="70" t="s">
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="67"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="72"/>
     </row>
     <row r="2" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
@@ -3052,12 +3071,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="77" t="s">
         <v>329</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="26" t="s">
@@ -3259,33 +3278,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3406,10 +3425,10 @@
         <v>35</v>
       </c>
       <c r="G3" s="53"/>
-      <c r="H3" s="75" t="s">
+      <c r="H3" s="65" t="s">
         <v>374</v>
       </c>
-      <c r="I3" s="75" t="s">
+      <c r="I3" s="65" t="s">
         <v>376</v>
       </c>
       <c r="J3" s="59"/>
@@ -3458,10 +3477,10 @@
       <c r="G4" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I4" s="77" t="s">
+      <c r="I4" s="67" t="s">
         <v>377</v>
       </c>
       <c r="J4" s="59"/>
@@ -3510,10 +3529,10 @@
       <c r="G5" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I5" s="77" t="s">
+      <c r="I5" s="67" t="s">
         <v>377</v>
       </c>
       <c r="J5" s="59"/>
@@ -3562,10 +3581,10 @@
       <c r="G6" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="76" t="s">
+      <c r="H6" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I6" s="77" t="s">
+      <c r="I6" s="67" t="s">
         <v>380</v>
       </c>
       <c r="J6" s="60" t="s">
@@ -3616,10 +3635,10 @@
       <c r="G7" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="76" t="s">
+      <c r="H7" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I7" s="77" t="s">
+      <c r="I7" s="67" t="s">
         <v>379</v>
       </c>
       <c r="J7" s="59"/>
@@ -3668,10 +3687,10 @@
       <c r="G8" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="76" t="s">
+      <c r="H8" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I8" s="76" t="s">
+      <c r="I8" s="66" t="s">
         <v>378</v>
       </c>
       <c r="J8" s="59"/>
@@ -3720,10 +3739,10 @@
       <c r="G9" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="76" t="s">
+      <c r="H9" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I9" s="75" t="s">
+      <c r="I9" s="65" t="s">
         <v>376</v>
       </c>
       <c r="J9" s="60" t="s">
@@ -3774,10 +3793,10 @@
       <c r="G10" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="76" t="s">
+      <c r="H10" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="66" t="s">
         <v>376</v>
       </c>
       <c r="J10" s="59"/>
@@ -3826,10 +3845,10 @@
       <c r="G11" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="76" t="s">
+      <c r="H11" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="I11" s="77" t="s">
+      <c r="I11" s="67" t="s">
         <v>380</v>
       </c>
       <c r="J11" s="60" t="s">
@@ -3880,7 +3899,7 @@
       <c r="G12" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="76" t="s">
+      <c r="H12" s="66" t="s">
         <v>375</v>
       </c>
       <c r="I12" s="51" t="s">
@@ -3969,33 +3988,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4864,33 +4883,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5012,7 +5031,7 @@
       </c>
       <c r="G3" s="53"/>
       <c r="H3" s="49"/>
-      <c r="I3" s="78" t="s">
+      <c r="I3" s="68" t="s">
         <v>376</v>
       </c>
       <c r="J3" s="59"/>
@@ -5698,33 +5717,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5846,7 +5865,7 @@
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="14"/>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="69" t="s">
         <v>376</v>
       </c>
       <c r="J3" s="30" t="s">
@@ -5898,7 +5917,7 @@
         <v>164</v>
       </c>
       <c r="H4" s="49"/>
-      <c r="I4" s="75" t="s">
+      <c r="I4" s="65" t="s">
         <v>376</v>
       </c>
       <c r="J4" s="60" t="s">
@@ -6957,33 +6976,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7806,33 +7825,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8175,33 +8194,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8322,8 +8341,10 @@
         <v>172</v>
       </c>
       <c r="G3" s="53"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="75" t="s">
+      <c r="H3" s="65" t="s">
+        <v>383</v>
+      </c>
+      <c r="I3" s="65" t="s">
         <v>381</v>
       </c>
       <c r="J3" s="59"/>
@@ -8372,7 +8393,9 @@
       <c r="G4" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H4" s="51"/>
+      <c r="H4" s="80" t="s">
+        <v>382</v>
+      </c>
       <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
@@ -8422,7 +8445,9 @@
       <c r="G5" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H5" s="51"/>
+      <c r="H5" s="80" t="s">
+        <v>382</v>
+      </c>
       <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
@@ -8472,7 +8497,9 @@
       <c r="G6" s="54" t="s">
         <v>278</v>
       </c>
-      <c r="H6" s="51"/>
+      <c r="H6" s="80" t="s">
+        <v>382</v>
+      </c>
       <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
@@ -8522,7 +8549,9 @@
       <c r="G7" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="H7" s="51"/>
+      <c r="H7" s="80" t="s">
+        <v>382</v>
+      </c>
       <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
@@ -8572,7 +8601,9 @@
       <c r="G8" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H8" s="51"/>
+      <c r="H8" s="80" t="s">
+        <v>382</v>
+      </c>
       <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
@@ -8651,33 +8682,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AE1" s="67"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="72"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/仕様書/プロト仕様書-プログラマ-.xlsx
+++ b/仕様書/プロト仕様書-プログラマ-.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanat\Desktop\MagnetRush\仕様書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\HAL_3\kamigame\MagnetRush\仕様書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197A9861-AAC8-4C7B-855A-E01CB732CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872066DA-01A8-4432-955D-016CF3D73C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="4320" windowWidth="21600" windowHeight="11835" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体ガント" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="390">
   <si>
     <t>← 全体ガントに戻る</t>
   </si>
@@ -753,9 +753,6 @@
     <t>雑魚敵</t>
   </si>
   <si>
-    <t>NavMeshベイク</t>
-  </si>
-  <si>
     <t>NavMesh上を敵がエラーなく歩行。</t>
   </si>
   <si>
@@ -793,9 +790,6 @@
   </si>
   <si>
     <t>No.64,No.39</t>
-  </si>
-  <si>
-    <t>敵Prefab化（Nested構成）</t>
   </si>
   <si>
     <t>Prefab配置で正常動作。サブPrefab個別編集可。</t>
@@ -1489,12 +1483,128 @@
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>蘇</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>ok
+ playerの反応はまだ出さない</t>
+    <rPh sb="11" eb="13">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>敵</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Prefab</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>化（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Nested</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>構成）</t>
+    </r>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <r>
+      <t>NavMesh</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ベイク</t>
+    </r>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>サブカテゴリ</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ok
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>いまの敵はすごく弱いですよ</t>
+    </r>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヨワ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1742,6 +1852,35 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1930,7 +2069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2117,6 +2256,9 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -2131,8 +2273,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2454,32 +2620,32 @@
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="75" t="s">
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="72"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="73"/>
     </row>
     <row r="2" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
@@ -2924,10 +3090,10 @@
         <v>60</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -2935,13 +3101,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="D2" s="42" t="s">
         <v>300</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -2949,13 +3115,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="D3" s="42" t="s">
         <v>303</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>304</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -2963,13 +3129,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>306</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>307</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -2980,10 +3146,10 @@
         <v>44</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -2991,13 +3157,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>311</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -3005,13 +3171,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="42" t="s">
         <v>314</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>315</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -3019,13 +3185,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>317</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -3033,13 +3199,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" s="42" t="s">
         <v>320</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>321</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -3047,13 +3213,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="42" t="s">
         <v>323</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>324</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
@@ -3061,35 +3227,35 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="D11" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="C11" s="42" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="78" t="s">
         <v>327</v>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="77" t="s">
-        <v>329</v>
-      </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B15" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="26" t="s">
         <v>330</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3100,10 +3266,10 @@
         <v>44</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3111,13 +3277,13 @@
         <v>2</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3128,10 +3294,10 @@
         <v>188</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3142,10 +3308,10 @@
         <v>165</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3156,10 +3322,10 @@
         <v>169</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3167,13 +3333,13 @@
         <v>6</v>
       </c>
       <c r="B21" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="43" t="s">
         <v>343</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>344</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3181,13 +3347,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="D22" s="43" t="s">
         <v>346</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>347</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3195,13 +3361,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3209,13 +3375,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="43" t="s">
         <v>351</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>352</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3226,10 +3392,10 @@
         <v>103</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.15">
@@ -3240,10 +3406,10 @@
         <v>202</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3278,33 +3444,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3413,10 +3579,10 @@
         <v>33</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E3" s="48" t="s">
         <v>34</v>
@@ -3426,10 +3592,10 @@
       </c>
       <c r="G3" s="53"/>
       <c r="H3" s="65" t="s">
+        <v>372</v>
+      </c>
+      <c r="I3" s="65" t="s">
         <v>374</v>
-      </c>
-      <c r="I3" s="65" t="s">
-        <v>376</v>
       </c>
       <c r="J3" s="59"/>
       <c r="K3" s="6"/>
@@ -3466,7 +3632,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>34</v>
@@ -3478,10 +3644,10 @@
         <v>38</v>
       </c>
       <c r="H4" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="I4" s="67" t="s">
         <v>375</v>
-      </c>
-      <c r="I4" s="67" t="s">
-        <v>377</v>
       </c>
       <c r="J4" s="59"/>
       <c r="K4" s="6"/>
@@ -3518,7 +3684,7 @@
         <v>39</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>34</v>
@@ -3530,10 +3696,10 @@
         <v>40</v>
       </c>
       <c r="H5" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="I5" s="67" t="s">
         <v>375</v>
-      </c>
-      <c r="I5" s="67" t="s">
-        <v>377</v>
       </c>
       <c r="J5" s="59"/>
       <c r="K5" s="6"/>
@@ -3570,7 +3736,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>34</v>
@@ -3582,10 +3748,10 @@
         <v>43</v>
       </c>
       <c r="H6" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J6" s="60" t="s">
         <v>44</v>
@@ -3624,7 +3790,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>34</v>
@@ -3636,10 +3802,10 @@
         <v>38</v>
       </c>
       <c r="H7" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I7" s="67" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J7" s="59"/>
       <c r="K7" s="2"/>
@@ -3676,7 +3842,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>34</v>
@@ -3688,10 +3854,10 @@
         <v>47</v>
       </c>
       <c r="H8" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I8" s="66" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J8" s="59"/>
       <c r="K8" s="2"/>
@@ -3728,7 +3894,7 @@
         <v>49</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E9" s="48" t="s">
         <v>34</v>
@@ -3740,10 +3906,10 @@
         <v>38</v>
       </c>
       <c r="H9" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I9" s="65" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J9" s="60" t="s">
         <v>50</v>
@@ -3782,7 +3948,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>34</v>
@@ -3794,10 +3960,10 @@
         <v>52</v>
       </c>
       <c r="H10" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I10" s="66" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J10" s="59"/>
       <c r="K10" s="2"/>
@@ -3846,10 +4012,10 @@
         <v>56</v>
       </c>
       <c r="H11" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I11" s="67" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J11" s="60" t="s">
         <v>44</v>
@@ -3900,7 +4066,7 @@
         <v>59</v>
       </c>
       <c r="H12" s="66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I12" s="51" t="s">
         <v>36</v>
@@ -3988,33 +4154,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4883,33 +5049,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5021,7 +5187,7 @@
         <v>123</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E3" s="48" t="s">
         <v>34</v>
@@ -5032,7 +5198,7 @@
       <c r="G3" s="53"/>
       <c r="H3" s="49"/>
       <c r="I3" s="68" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J3" s="59"/>
       <c r="K3" s="6"/>
@@ -5717,33 +5883,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5855,7 +6021,7 @@
         <v>160</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>34</v>
@@ -5866,7 +6032,7 @@
       <c r="G3" s="17"/>
       <c r="H3" s="14"/>
       <c r="I3" s="69" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J3" s="30" t="s">
         <v>44</v>
@@ -5918,7 +6084,7 @@
       </c>
       <c r="H4" s="49"/>
       <c r="I4" s="65" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J4" s="60" t="s">
         <v>165</v>
@@ -6359,7 +6525,7 @@
         <v>192</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E13" s="50" t="s">
         <v>34</v>
@@ -6755,7 +6921,7 @@
         <v>56</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C21" s="44" t="s">
         <v>216</v>
@@ -6970,47 +7136,47 @@
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="9" max="9" width="32.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="32" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>2</v>
+        <v>388</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>387</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>3</v>
@@ -7111,10 +7277,10 @@
         <v>232</v>
       </c>
       <c r="C3" s="64" t="s">
+        <v>386</v>
+      </c>
+      <c r="D3" s="39" t="s">
         <v>233</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>234</v>
       </c>
       <c r="E3" s="48" t="s">
         <v>34</v>
@@ -7123,12 +7289,14 @@
         <v>35</v>
       </c>
       <c r="G3" s="53"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="81" t="s">
+        <v>382</v>
+      </c>
       <c r="I3" s="49" t="s">
-        <v>36</v>
+        <v>383</v>
       </c>
       <c r="J3" s="60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -7161,10 +7329,10 @@
         <v>232</v>
       </c>
       <c r="C4" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>236</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>237</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>34</v>
@@ -7173,9 +7341,11 @@
         <v>35</v>
       </c>
       <c r="G4" s="57"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="51" t="s">
-        <v>36</v>
+      <c r="H4" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="I4" s="67" t="s">
+        <v>383</v>
       </c>
       <c r="J4" s="59"/>
       <c r="K4" s="2"/>
@@ -7209,10 +7379,10 @@
         <v>232</v>
       </c>
       <c r="C5" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>238</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>239</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>34</v>
@@ -7221,11 +7391,13 @@
         <v>42</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="51" t="s">
-        <v>36</v>
+        <v>239</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="I5" s="67" t="s">
+        <v>383</v>
       </c>
       <c r="J5" s="60" t="s">
         <v>44</v>
@@ -7261,10 +7433,10 @@
         <v>232</v>
       </c>
       <c r="C6" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>241</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>242</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>34</v>
@@ -7273,11 +7445,13 @@
         <v>42</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="51" t="s">
-        <v>36</v>
+        <v>242</v>
+      </c>
+      <c r="H6" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="I6" s="86" t="s">
+        <v>384</v>
       </c>
       <c r="J6" s="59"/>
       <c r="K6" s="2"/>
@@ -7311,10 +7485,10 @@
         <v>232</v>
       </c>
       <c r="C7" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>244</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>245</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>34</v>
@@ -7323,11 +7497,13 @@
         <v>35</v>
       </c>
       <c r="G7" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="51" t="s">
-        <v>36</v>
+        <v>245</v>
+      </c>
+      <c r="H7" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="I7" s="87" t="s">
+        <v>389</v>
       </c>
       <c r="J7" s="60" t="s">
         <v>165</v>
@@ -7355,18 +7531,18 @@
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
     </row>
-    <row r="8" spans="1:32" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:32" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18">
         <v>68</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="46" t="s">
-        <v>247</v>
+      <c r="C8" s="89" t="s">
+        <v>385</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>34</v>
@@ -7375,11 +7551,13 @@
         <v>35</v>
       </c>
       <c r="G8" s="54" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="51" t="s">
-        <v>36</v>
+        <v>247</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="I8" s="88" t="s">
+        <v>383</v>
       </c>
       <c r="J8" s="59"/>
       <c r="K8" s="2"/>
@@ -7410,13 +7588,13 @@
         <v>69</v>
       </c>
       <c r="B9" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="39" t="s">
         <v>250</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>251</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>252</v>
       </c>
       <c r="E9" s="48" t="s">
         <v>34</v>
@@ -7425,9 +7603,11 @@
         <v>42</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>253</v>
-      </c>
-      <c r="H9" s="14"/>
+        <v>251</v>
+      </c>
+      <c r="H9" s="83" t="s">
+        <v>382</v>
+      </c>
       <c r="I9" s="49" t="s">
         <v>36</v>
       </c>
@@ -7460,13 +7640,13 @@
         <v>70</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C10" s="45" t="s">
         <v>192</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>34</v>
@@ -7475,9 +7655,11 @@
         <v>35</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>255</v>
-      </c>
-      <c r="H10" s="18"/>
+        <v>253</v>
+      </c>
+      <c r="H10" s="82" t="s">
+        <v>382</v>
+      </c>
       <c r="I10" s="51" t="s">
         <v>36</v>
       </c>
@@ -7507,18 +7689,18 @@
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
     </row>
-    <row r="11" spans="1:32" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:32" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="18">
         <v>71</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E11" s="56" t="s">
         <v>106</v>
@@ -7529,7 +7711,9 @@
       <c r="G11" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="H11" s="18"/>
+      <c r="H11" s="82" t="s">
+        <v>382</v>
+      </c>
       <c r="I11" s="51" t="s">
         <v>36</v>
       </c>
@@ -7562,13 +7746,13 @@
         <v>72</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="D12" s="39" t="s">
         <v>258</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>259</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>260</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>55</v>
@@ -7577,7 +7761,9 @@
         <v>42</v>
       </c>
       <c r="G12" s="53"/>
-      <c r="H12" s="49"/>
+      <c r="H12" s="85" t="s">
+        <v>382</v>
+      </c>
       <c r="I12" s="49" t="s">
         <v>36</v>
       </c>
@@ -7610,13 +7796,13 @@
         <v>73</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E13" s="52" t="s">
         <v>55</v>
@@ -7625,9 +7811,11 @@
         <v>42</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="H13" s="51"/>
+        <v>261</v>
+      </c>
+      <c r="H13" s="84" t="s">
+        <v>382</v>
+      </c>
       <c r="I13" s="51" t="s">
         <v>36</v>
       </c>
@@ -7662,13 +7850,13 @@
         <v>74</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E14" s="52" t="s">
         <v>55</v>
@@ -7677,9 +7865,11 @@
         <v>35</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>266</v>
-      </c>
-      <c r="H14" s="51"/>
+        <v>264</v>
+      </c>
+      <c r="H14" s="84" t="s">
+        <v>382</v>
+      </c>
       <c r="I14" s="51" t="s">
         <v>36</v>
       </c>
@@ -7714,13 +7904,13 @@
         <v>75</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C15" s="46" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E15" s="52" t="s">
         <v>55</v>
@@ -7729,9 +7919,11 @@
         <v>35</v>
       </c>
       <c r="G15" s="54" t="s">
-        <v>269</v>
-      </c>
-      <c r="H15" s="51"/>
+        <v>267</v>
+      </c>
+      <c r="H15" s="84" t="s">
+        <v>382</v>
+      </c>
       <c r="I15" s="51" t="s">
         <v>36</v>
       </c>
@@ -7825,33 +8017,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8194,33 +8386,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8329,10 +8521,10 @@
         <v>74</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E3" s="48" t="s">
         <v>34</v>
@@ -8342,10 +8534,10 @@
       </c>
       <c r="G3" s="53"/>
       <c r="H3" s="65" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I3" s="65" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J3" s="59"/>
       <c r="K3" s="6"/>
@@ -8379,10 +8571,10 @@
         <v>74</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E4" s="52" t="s">
         <v>55</v>
@@ -8391,10 +8583,10 @@
         <v>42</v>
       </c>
       <c r="G4" s="54" t="s">
-        <v>273</v>
-      </c>
-      <c r="H4" s="80" t="s">
-        <v>382</v>
+        <v>271</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="I4" s="51" t="s">
         <v>36</v>
@@ -8431,10 +8623,10 @@
         <v>74</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E5" s="52" t="s">
         <v>55</v>
@@ -8443,10 +8635,10 @@
         <v>42</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>273</v>
-      </c>
-      <c r="H5" s="80" t="s">
-        <v>382</v>
+        <v>271</v>
+      </c>
+      <c r="H5" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="I5" s="51" t="s">
         <v>36</v>
@@ -8483,10 +8675,10 @@
         <v>74</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E6" s="52" t="s">
         <v>55</v>
@@ -8495,10 +8687,10 @@
         <v>42</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>278</v>
-      </c>
-      <c r="H6" s="80" t="s">
-        <v>382</v>
+        <v>276</v>
+      </c>
+      <c r="H6" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="I6" s="51" t="s">
         <v>36</v>
@@ -8535,10 +8727,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E7" s="52" t="s">
         <v>55</v>
@@ -8547,10 +8739,10 @@
         <v>35</v>
       </c>
       <c r="G7" s="54" t="s">
-        <v>281</v>
-      </c>
-      <c r="H7" s="80" t="s">
-        <v>382</v>
+        <v>279</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="I7" s="51" t="s">
         <v>36</v>
@@ -8587,10 +8779,10 @@
         <v>74</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>34</v>
@@ -8599,16 +8791,16 @@
         <v>42</v>
       </c>
       <c r="G8" s="54" t="s">
-        <v>273</v>
-      </c>
-      <c r="H8" s="80" t="s">
-        <v>382</v>
+        <v>271</v>
+      </c>
+      <c r="H8" s="70" t="s">
+        <v>380</v>
       </c>
       <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
       <c r="J8" s="60" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -8682,33 +8874,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="73"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8814,13 +9006,13 @@
         <v>88</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="D3" s="38" t="s">
         <v>284</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>286</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>55</v>
@@ -8862,13 +9054,13 @@
         <v>89</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E4" s="52" t="s">
         <v>55</v>
@@ -8877,7 +9069,7 @@
         <v>35</v>
       </c>
       <c r="G4" s="54" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H4" s="51"/>
       <c r="I4" s="51" t="s">
@@ -8914,13 +9106,13 @@
         <v>90</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="38" t="s">
         <v>290</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>292</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>55</v>
@@ -8929,7 +9121,7 @@
         <v>42</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H5" s="49"/>
       <c r="I5" s="49" t="s">
@@ -8964,13 +9156,13 @@
         <v>91</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E6" s="56" t="s">
         <v>106</v>
@@ -9014,13 +9206,13 @@
         <v>92</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>106</v>

--- a/仕様書/プロト仕様書-プログラマ-.xlsx
+++ b/仕様書/プロト仕様書-プログラマ-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\HAL_3\kamigame\MagnetRush\仕様書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872066DA-01A8-4432-955D-016CF3D73C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3AFFA6-C864-4B37-9E29-4B117FEA8505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2069,7 +2069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2259,20 +2259,6 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2299,6 +2285,23 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2620,32 +2623,32 @@
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="76" t="s">
+      <c r="C1" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="76" t="s">
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="73"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="82"/>
     </row>
     <row r="2" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
@@ -3237,12 +3240,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="87" t="s">
         <v>327</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="89"/>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="26" t="s">
@@ -3444,33 +3447,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4154,33 +4157,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5049,33 +5052,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5883,33 +5886,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7142,33 +7145,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7289,7 +7292,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="53"/>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="71" t="s">
         <v>382</v>
       </c>
       <c r="I3" s="49" t="s">
@@ -7341,7 +7344,7 @@
         <v>35</v>
       </c>
       <c r="G4" s="57"/>
-      <c r="H4" s="82" t="s">
+      <c r="H4" s="72" t="s">
         <v>382</v>
       </c>
       <c r="I4" s="67" t="s">
@@ -7393,7 +7396,7 @@
       <c r="G5" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="H5" s="82" t="s">
+      <c r="H5" s="72" t="s">
         <v>382</v>
       </c>
       <c r="I5" s="67" t="s">
@@ -7447,10 +7450,10 @@
       <c r="G6" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="H6" s="82" t="s">
+      <c r="H6" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="I6" s="86" t="s">
+      <c r="I6" s="76" t="s">
         <v>384</v>
       </c>
       <c r="J6" s="59"/>
@@ -7499,10 +7502,10 @@
       <c r="G7" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="H7" s="82" t="s">
+      <c r="H7" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="I7" s="87" t="s">
+      <c r="I7" s="77" t="s">
         <v>389</v>
       </c>
       <c r="J7" s="60" t="s">
@@ -7538,7 +7541,7 @@
       <c r="B8" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="79" t="s">
         <v>385</v>
       </c>
       <c r="D8" s="36" t="s">
@@ -7553,10 +7556,10 @@
       <c r="G8" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="H8" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="I8" s="88" t="s">
+      <c r="I8" s="78" t="s">
         <v>383</v>
       </c>
       <c r="J8" s="59"/>
@@ -7605,11 +7608,11 @@
       <c r="G9" s="55" t="s">
         <v>251</v>
       </c>
-      <c r="H9" s="83" t="s">
+      <c r="H9" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="I9" s="49" t="s">
-        <v>36</v>
+      <c r="I9" s="90" t="s">
+        <v>383</v>
       </c>
       <c r="J9" s="59"/>
       <c r="K9" s="2"/>
@@ -7657,11 +7660,11 @@
       <c r="G10" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="H10" s="82" t="s">
+      <c r="H10" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="I10" s="51" t="s">
-        <v>36</v>
+      <c r="I10" s="78" t="s">
+        <v>383</v>
       </c>
       <c r="J10" s="60" t="s">
         <v>165</v>
@@ -7711,11 +7714,11 @@
       <c r="G11" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="H11" s="82" t="s">
+      <c r="H11" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="I11" s="51" t="s">
-        <v>36</v>
+      <c r="I11" s="78" t="s">
+        <v>383</v>
       </c>
       <c r="J11" s="59"/>
       <c r="K11" s="2"/>
@@ -7761,11 +7764,11 @@
         <v>42</v>
       </c>
       <c r="G12" s="53"/>
-      <c r="H12" s="85" t="s">
+      <c r="H12" s="75" t="s">
         <v>382</v>
       </c>
-      <c r="I12" s="49" t="s">
-        <v>36</v>
+      <c r="I12" s="90" t="s">
+        <v>383</v>
       </c>
       <c r="J12" s="59"/>
       <c r="K12" s="2"/>
@@ -7813,7 +7816,7 @@
       <c r="G13" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="H13" s="84" t="s">
+      <c r="H13" s="74" t="s">
         <v>382</v>
       </c>
       <c r="I13" s="51" t="s">
@@ -7867,11 +7870,11 @@
       <c r="G14" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="H14" s="84" t="s">
+      <c r="H14" s="74" t="s">
         <v>382</v>
       </c>
-      <c r="I14" s="51" t="s">
-        <v>36</v>
+      <c r="I14" s="78" t="s">
+        <v>383</v>
       </c>
       <c r="J14" s="60" t="s">
         <v>165</v>
@@ -7921,11 +7924,11 @@
       <c r="G15" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="H15" s="84" t="s">
+      <c r="H15" s="74" t="s">
         <v>382</v>
       </c>
-      <c r="I15" s="51" t="s">
-        <v>36</v>
+      <c r="I15" s="78" t="s">
+        <v>383</v>
       </c>
       <c r="J15" s="59"/>
       <c r="K15" s="2"/>
@@ -8017,33 +8020,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8386,33 +8389,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8874,33 +8877,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/仕様書/プロト仕様書-プログラマ-.xlsx
+++ b/仕様書/プロト仕様書-プログラマ-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\HAL_3\kamigame\MagnetRush\仕様書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3AFFA6-C864-4B37-9E29-4B117FEA8505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3581660-26E1-4E09-B939-8DAC507D0260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7819,8 +7819,8 @@
       <c r="H13" s="74" t="s">
         <v>382</v>
       </c>
-      <c r="I13" s="51" t="s">
-        <v>36</v>
+      <c r="I13" s="78" t="s">
+        <v>383</v>
       </c>
       <c r="J13" s="60" t="s">
         <v>44</v>
